--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 14/08/2026</t>
+As of 17/08/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001450008</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242067</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>660.0</v>
+        <v>400.0</v>
       </c>
       <c r="N3" t="n">
-        <v>660.0</v>
+        <v>400.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001445059</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242066</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000000541229</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Optimum Global Care</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,155 +791,17 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>120.0</v>
+        <v>718.8</v>
       </c>
       <c r="N4" t="n">
-        <v>120.0</v>
+        <v>718.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>510492000001450008</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>242067</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>510492000000327139</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>BATHROOMS LONDON LIMITED</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>510492000001450025</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>242068</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>510492000000122647</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>718.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>718.8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -948,7 +810,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A7:O7"/>
+    <mergeCell ref="A5:O5"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 17/08/2026</t>
+As of 20/08/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001450008</t>
+          <t>510492000001450155</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242067</t>
+          <t>242070</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000001450146</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>Mr. Phone Mobile &amp; Vape</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>400.0</v>
+        <v>150.0</v>
       </c>
       <c r="N3" t="n">
-        <v>400.0</v>
+        <v>150.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001460001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242071</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000001436106</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,17 +791,293 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>718.8</v>
+        <v>100.0</v>
       </c>
       <c r="N4" t="n">
-        <v>718.8</v>
+        <v>100.0</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>510492000001460037</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>242072</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>510492000001413024</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>88 DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>510492000001460054</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>242073</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>510492000001252008</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Surge Productions Ltd</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>510492000001460071</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>242074</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>510492000000822033</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Sofiya Designs Limited</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1080.0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1080.0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>510492000001460089</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>242075</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>510492000000639001</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>De'Osa Engineering Services</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -810,7 +1086,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A9:O9"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 21/08/2026</t>
+As of 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001450155</t>
+          <t>510492000001460037</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242070</t>
+          <t>242072</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001450146</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Mr. Phone Mobile &amp; Vape</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>150.0</v>
+        <v>100.0</v>
       </c>
       <c r="N3" t="n">
-        <v>150.0</v>
+        <v>100.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001460001</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242071</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000001436106</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>100.0</v>
+        <v>120.0</v>
       </c>
       <c r="N4" t="n">
-        <v>100.0</v>
+        <v>120.0</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>
@@ -803,7 +803,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>510492000001460037</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242072</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>100.0</v>
+        <v>250.0</v>
       </c>
       <c r="N5" t="n">
-        <v>100.0</v>
+        <v>250.0</v>
       </c>
       <c r="O5" t="n">
         <v>1.0</v>
@@ -872,7 +872,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>510492000001460054</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>242073</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>510492000001252008</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Surge Productions Ltd</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>300.0</v>
+        <v>240.0</v>
       </c>
       <c r="N6" t="n">
-        <v>300.0</v>
+        <v>240.0</v>
       </c>
       <c r="O6" t="n">
         <v>1.0</v>
@@ -941,7 +941,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>510492000001460071</t>
+          <t>510492000001467184</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -979,17 +979,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>242074</t>
+          <t>242079</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>510492000000822033</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sofiya Designs Limited</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -998,293 +998,17 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1080.0</v>
+        <v>150.0</v>
       </c>
       <c r="N7" t="n">
-        <v>1080.0</v>
+        <v>150.0</v>
       </c>
       <c r="O7" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>510492000001460089</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>242075</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>510492000000639001</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>De'Osa Engineering Services</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>510492000001460115</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>242076</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>510492000001460106</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>MOUNTAINS OF GLORY</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>510492000001460138</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>242077</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>510492000000386033</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ALPHA EUROPE LTD</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>510492000001460166</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>242078</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>510492000001158053</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>PRIME GARDEN DESIGN LTD</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>270.0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>270.0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1293,7 +1017,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 24/08/2026</t>
+As of 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001460037</t>
+          <t>510492000001474010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242072</t>
+          <t>242080</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000001474001</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>First Class Learning Reading Central</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,293 +722,17 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>100.0</v>
+        <v>270.0</v>
       </c>
       <c r="N3" t="n">
-        <v>100.0</v>
+        <v>270.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>510492000001460089</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>242075</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>510492000000639001</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>De'Osa Engineering Services</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>510492000001460115</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>242076</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>510492000001460106</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>MOUNTAINS OF GLORY</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>510492000001460138</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>242077</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>510492000000386033</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ALPHA EUROPE LTD</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>510492000001467184</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>242079</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>510492000000256001</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>150.0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>150.0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1017,7 +741,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A4:O4"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 27/08/2026</t>
+As of 01/09/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001474010</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242080</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001474001</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>First Class Learning Reading Central</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,17 +722,431 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>270.0</v>
+        <v>240.0</v>
       </c>
       <c r="N3" t="n">
-        <v>270.0</v>
+        <v>240.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>510492000001474010</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>242080</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>510492000001474001</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>First Class Learning Reading Central</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>270.0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>270.0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>510492000001477103</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>242081</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>510492000000541229</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Optimum Global Care</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>510492000001482001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>242082</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>510492000001057001</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Corby Motors Ltd</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>555.0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>555.0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>510492000001482018</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>242083</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>510492000001413024</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>88 DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>510492000001488015</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>242084</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>510492000001488006</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>510492000001367115</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>242017</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>310.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>310.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -741,7 +1155,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A10:O10"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
